--- a/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_1_site.xlsx
+++ b/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_1_site.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
@@ -501,20 +501,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col width="28" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
     <col width="14.5" customWidth="1" style="8" min="2" max="2"/>
     <col width="47" customWidth="1" style="8" min="3" max="3"/>
     <col width="41.25" customWidth="1" style="8" min="4" max="4"/>
-    <col width="12.625" customWidth="1" style="8" min="5" max="5"/>
-    <col width="9.625" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
-    <col width="25.125" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
-    <col width="20.375" customWidth="1" style="8" min="8" max="8"/>
-    <col width="27.625" customWidth="1" style="8" min="9" max="9"/>
+    <col width="12.58203125" customWidth="1" style="8" min="5" max="5"/>
+    <col width="9.58203125" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="25.08203125" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="20.33203125" customWidth="1" style="8" min="8" max="8"/>
+    <col width="27.58203125" customWidth="1" style="8" min="9" max="9"/>
     <col width="9.75" customWidth="1" style="8" min="10" max="10"/>
     <col width="8.25" bestFit="1" customWidth="1" style="8" min="11" max="11"/>
-    <col width="53.625" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
+    <col width="53.58203125" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
     <col width="14.5" customWidth="1" style="8" min="13" max="13"/>
     <col width="18" bestFit="1" customWidth="1" style="8" min="14" max="17"/>
     <col width="11" customWidth="1" style="8" min="18" max="16384"/>
@@ -607,7 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="2" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>select_one recorder_list</t>
@@ -843,7 +843,7 @@
       <c r="O7" s="25" t="n"/>
       <c r="Q7" s="26" t="n"/>
     </row>
-    <row r="8" ht="31.5" customFormat="1" customHeight="1" s="7">
+    <row r="8" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>text</t>
@@ -882,7 +882,7 @@
       <c r="P8" s="25" t="n"/>
       <c r="Q8" s="25" t="n"/>
     </row>
-    <row r="9" ht="31.5" customFormat="1" customHeight="1" s="7">
+    <row r="9" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>select_one school</t>
@@ -895,7 +895,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Select your school</t>
+          <t>Select your school/site</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -925,7 +925,7 @@
       <c r="P9" s="25" t="n"/>
       <c r="Q9" s="25" t="n"/>
     </row>
-    <row r="10" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="10" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>text</t>
@@ -938,7 +938,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Enter the name of the replacement School</t>
+          <t>Enter the name of the replacement site/School</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -964,7 +964,7 @@
       <c r="P10" s="25" t="n"/>
       <c r="Q10" s="25" t="n"/>
     </row>
-    <row r="11" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="11" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>select_one school_id</t>
@@ -1007,7 +1007,7 @@
       <c r="P11" s="25" t="n"/>
       <c r="Q11" s="25" t="n"/>
     </row>
-    <row r="12" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="12" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>select_one school_id2</t>
@@ -1050,7 +1050,7 @@
       <c r="P12" s="25" t="n"/>
       <c r="Q12" s="25" t="n"/>
     </row>
-    <row r="13" ht="63" customFormat="1" customHeight="1" s="7">
+    <row r="13" ht="62" customFormat="1" customHeight="1" s="7">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>text</t>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Q13" s="25" t="n"/>
     </row>
-    <row r="14" ht="63" customFormat="1" customHeight="1" s="7">
+    <row r="14" ht="62" customFormat="1" customHeight="1" s="7">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>text</t>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="15" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>select_one site_type</t>
@@ -1195,7 +1195,7 @@
       <c r="P15" s="25" t="n"/>
       <c r="Q15" s="25" t="n"/>
     </row>
-    <row r="16" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="16" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>select_one site_type_2</t>
@@ -1273,7 +1273,7 @@
       <c r="P17" s="25" t="n"/>
       <c r="Q17" s="26" t="n"/>
     </row>
-    <row r="18" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="18" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>integer</t>
@@ -1308,7 +1308,7 @@
       <c r="P18" s="25" t="n"/>
       <c r="Q18" s="26" t="n"/>
     </row>
-    <row r="19" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="19" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>integer</t>
@@ -1343,7 +1343,7 @@
       <c r="P19" s="25" t="n"/>
       <c r="Q19" s="26" t="n"/>
     </row>
-    <row r="20" ht="47.25" customFormat="1" customHeight="1" s="7">
+    <row r="20" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>integer</t>
@@ -1716,13 +1716,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J673"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="16.375" customWidth="1" style="2" min="1" max="1"/>
-    <col width="18.625" customWidth="1" min="2" max="2"/>
-    <col width="19.125" customWidth="1" min="3" max="3"/>
+    <col width="16.33203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="18.58203125" customWidth="1" min="2" max="2"/>
+    <col width="19.08203125" customWidth="1" min="3" max="3"/>
     <col width="19.75" customWidth="1" min="4" max="4"/>
-    <col width="17.875" customWidth="1" min="5" max="6"/>
+    <col width="17.83203125" customWidth="1" min="5" max="6"/>
     <col width="13.25" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -16343,12 +16343,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="44.125" customWidth="1" min="1" max="1"/>
+    <col width="44.08203125" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="15.875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="22.125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="15.83203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="22.08203125" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16376,7 +16376,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>(Demo) 1. ITAS LF-ONCHO Site Form</t>
+          <t>(Uganda) 1. ITAS LF-ONCHO Site Form</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
